--- a/Fischer_Tropsch/Leuna_FischerTropsch_4_Naphta_Bio_H2_Brownfield/Datenbank.xlsx
+++ b/Fischer_Tropsch/Leuna_FischerTropsch_4_Naphta_Bio_H2_Brownfield/Datenbank.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Leuna_4_FischerTropsch_Naphta_Bio_H2_Brownfield\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Leuna_FischerTropsch_4_Naphta_Bio_H2_Brownfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9038C15-B73D-407C-97DA-DAA57B97AFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AC1514-FAC3-4E5D-95A9-5EDC640DDFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1672,9 +1672,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1683,6 +1680,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2170,7 +2170,7 @@
         <v>302</v>
       </c>
       <c r="E8" s="16">
-        <v>38.99</v>
+        <v>10</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>313</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="44"/>
-      <c r="B82" s="58" t="s">
+      <c r="B82" s="57" t="s">
         <v>404</v>
       </c>
       <c r="C82" s="15" t="s">
@@ -4509,7 +4509,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="44"/>
-      <c r="B83" s="57"/>
+      <c r="B83" s="56"/>
       <c r="C83" s="1" t="s">
         <v>407</v>
       </c>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="44"/>
-      <c r="B84" s="59"/>
+      <c r="B84" s="58"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
       <c r="E84" s="38"/>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="44"/>
-      <c r="B85" s="57" t="s">
+      <c r="B85" s="56" t="s">
         <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -4547,7 +4547,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="44"/>
-      <c r="B86" s="57"/>
+      <c r="B86" s="56"/>
       <c r="C86" s="1" t="s">
         <v>380</v>
       </c>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="44"/>
-      <c r="B87" s="57"/>
+      <c r="B87" s="56"/>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -5407,7 +5407,7 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="44"/>
-      <c r="B154" s="56" t="s">
+      <c r="B154" s="59" t="s">
         <v>355</v>
       </c>
       <c r="C154" s="1" t="s">
@@ -5422,7 +5422,7 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="44"/>
-      <c r="B155" s="56"/>
+      <c r="B155" s="59"/>
       <c r="C155" s="1" t="s">
         <v>357</v>
       </c>
@@ -5435,15 +5435,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="A47:A78"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B47:B56"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A123:A155"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="B133:B147"/>
+    <mergeCell ref="B126:B132"/>
     <mergeCell ref="B120:B122"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="A79:A107"/>
@@ -5456,12 +5453,15 @@
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B85:B87"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B148:B153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A123:A155"/>
-    <mergeCell ref="B123:B125"/>
-    <mergeCell ref="B133:B147"/>
-    <mergeCell ref="B126:B132"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="A47:A78"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B47:B56"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="B34:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
